--- a/CardArchive/Tools/DataExport/Rarity.xlsx
+++ b/CardArchive/Tools/DataExport/Rarity.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="References" sheetId="1" r:id="rId1"/>
-    <sheet name="Enums" sheetId="2" r:id="rId2"/>
-    <sheet name="Rarity" sheetId="3" r:id="rId3"/>
+    <sheet name="Reference" sheetId="1" r:id="rId1"/>
+    <sheet name="Enum" sheetId="2" r:id="rId2"/>
+    <sheet name="_컬럼 설명" sheetId="3" r:id="rId3"/>
+    <sheet name="Rarity" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -13,30 +14,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">File</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
+      <c r="A1"/>
+      <c r="B1"/>
+      <c r="C1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -45,13 +25,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
   </sheetData>
 </worksheet>
 </file>
@@ -59,137 +33,330 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
+    <row r="1"/>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TableName</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">설명</t>
+        </is>
+      </c>
+      <c r="C3"/>
+    </row>
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">설명</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!EndField</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Id</t>
+        </is>
+      </c>
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+    </row>
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+    </row>
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rank</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+    </row>
+    <row r="9">
+      <c r="A9"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!EndTable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1"/>
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Table</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rarity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!AutoKey;!GenerateCsEnum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">icon</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">rank</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">title</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">!EndTable</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">_ID_Rarity</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">path</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">string</t>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!EndField</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Id</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!Int</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">!String</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">common</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Sprites/Icons/rarity_common.png</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="F4">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">Common</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5"/>
+      <c r="B5"/>
+      <c r="C5"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">mythic</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Sprites/Icons/rarity_mythic.png</t>
         </is>
       </c>
-      <c r="C4">
+      <c r="F5">
         <v>4</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mythic</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">rare</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Sprites/Icons/rarity_rare.png</t>
         </is>
       </c>
-      <c r="C5">
+      <c r="F6">
         <v>3</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">Rare</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">uncommon</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/TcgEngine/Sprites/Icons/rarity_uncommon.png</t>
         </is>
       </c>
-      <c r="C6">
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">Uncommon</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">!EndTable</t>
         </is>

--- a/CardArchive/Tools/DataExport/Rarity.xlsx
+++ b/CardArchive/Tools/DataExport/Rarity.xlsx
@@ -10,6 +10,44 @@
 </workbook>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font/>
+    <font>
+      <b/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>
@@ -58,37 +96,37 @@
     </row>
     <row r="4">
       <c r="A4"/>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">No</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Name</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Type</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Detail</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">설명</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">비고</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">!EndField</t>
         </is>
